--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -778,6 +778,8 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,7 +792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -845,6 +847,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -887,6 +899,12 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>-8.965678804109272</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.05770340450086555</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -929,6 +947,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K7" s="5" t="n">
+        <v>-29.47574044968526</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -971,6 +993,10 @@
           <t>Aceptable</t>
         </is>
       </c>
+      <c r="K8" s="5" t="n">
+        <v>-30.74031403122097</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1013,6 +1039,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K9" s="5" t="n">
+        <v>-9.622733583515469</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1055,6 +1085,12 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K10" s="5" t="n">
+        <v>-9.248977206312098</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0.1356767137012607</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1097,6 +1133,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1139,6 +1177,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1181,6 +1221,8 @@
           <t>Aceptable</t>
         </is>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1223,6 +1265,8 @@
           <t>Aceptable</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1265,6 +1309,10 @@
           <t>Exitosa</t>
         </is>
       </c>
+      <c r="K15" s="5" t="n">
+        <v>-8.563922344672292</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1277,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1290,6 +1338,8 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1302,7 +1352,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1357,6 +1407,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1399,6 +1459,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>3.451963622259546</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1441,6 +1505,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="n">
+        <v>0.03099040237947146</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1483,6 +1551,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1525,6 +1595,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1567,6 +1639,10 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K10" s="5" t="n">
+        <v>-5.374945299757328</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1609,6 +1685,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1651,6 +1729,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1693,6 +1773,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1735,6 +1817,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n">
+        <v>0.1155882822636469</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1777,6 +1863,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1789,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1802,6 +1890,8 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1814,7 +1904,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1869,6 +1959,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1911,6 +2011,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1953,6 +2055,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1995,6 +2099,10 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="n">
+        <v>0.02534218211934963</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2037,6 +2145,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2079,6 +2189,10 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n">
+        <v>-0.2839562791408698</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2121,6 +2235,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2163,6 +2279,10 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>0.07256894049346879</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2205,6 +2325,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2247,6 +2369,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2288,6 +2412,10 @@
         <is>
           <t>Sin Conversión</t>
         </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="n">
+        <v>-0.3452819045022943</v>
       </c>
     </row>
   </sheetData>
@@ -2301,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2314,6 +2442,8 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2326,7 +2456,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2381,6 +2511,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2423,6 +2563,12 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>-2.665161688796858</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.1261034047919294</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2465,6 +2611,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2507,6 +2655,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="n">
+        <v>-0.03455666200629899</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2549,6 +2701,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="n">
+        <v>-0.2989990861091568</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2591,6 +2747,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n">
+        <v>0.08738718485782279</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2633,6 +2793,12 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K11" s="5" t="n">
+        <v>-0.1590329135765178</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>-0.1139476022929844</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2675,6 +2841,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>0.1248439450686642</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2717,6 +2887,12 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K13" s="5" t="n">
+        <v>-8.965678804109272</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.05770340450086555</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2759,6 +2935,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n">
+        <v>0.03099040237947146</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2800,6 +2980,10 @@
         <is>
           <t>Crítica</t>
         </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="n">
+        <v>-0.1661919814716284</v>
       </c>
     </row>
   </sheetData>
@@ -2836,7 +3020,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4348,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7628,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +150,8 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -533,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -792,7 +794,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -874,19 +876,19 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>794</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.01133501259445844</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.001259445843828715</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -922,19 +924,19 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>1020</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>183</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.1794117647058824</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.004901960784313725</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -968,19 +970,19 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>191</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.2827225130890053</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0.02094240837696335</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1014,19 +1016,19 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>385</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>211</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.548051948051948</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.005194805194805195</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1060,19 +1062,19 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>481</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>264</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.5488565488565489</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0.002079002079002079</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1108,19 +1110,19 @@
           <t>Okinawa Area</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>166</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.5542168674698795</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0.01204819277108434</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1152,19 +1154,19 @@
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>162</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.5802469135802469</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.006172839506172839</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1196,19 +1198,19 @@
           <t>Jersey City Area</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0.01666666666666667</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1240,19 +1242,19 @@
           <t>London Area</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>168</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>108</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0.01785714285714286</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1284,19 +1286,19 @@
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>227</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>149</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.6563876651982379</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0.03524229074889868</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1352,7 +1354,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1434,19 +1436,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>10425</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>6886</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.6605275779376499</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.005275779376498801</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1480,19 +1482,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>6292</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>6135</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.9750476795931341</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.001271455816910362</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1526,19 +1528,19 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>2899</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>2748</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.9479130734736116</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0.007588823732321491</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1570,19 +1572,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>2781</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>2773</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.9971233369291622</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.003595828838547285</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1614,19 +1616,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>2754</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>2434</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.8838053740014524</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0.01053013798111837</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -1660,19 +1662,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>2745</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>2718</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.9901639344262295</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0.01493624772313297</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1704,19 +1706,19 @@
           <t>Budapest Area</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>2714</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>2625</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.9672070744288872</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.004789977892409728</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -1748,19 +1750,19 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>2640</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>2566</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.9719696969696969</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0.008712121212121213</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1792,19 +1794,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>2598</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>2575</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.9911470361816782</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0.003464203233256351</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -1838,19 +1840,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>2467</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>2454</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.9947304418321848</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0.01175516822051074</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -1904,7 +1906,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1986,19 +1988,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>2079</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>285</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.1370851370851371</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -2030,19 +2032,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>1582</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>318</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.2010113780025284</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -2074,19 +2076,19 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>1409</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>1392</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.9879347054648687</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2120,19 +2122,19 @@
           <t>Jakarta Area</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>1201</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>1201</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2164,19 +2166,19 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>1027</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>1027</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2210,19 +2212,19 @@
           <t>Antalya Area</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>1017</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>1011</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.9941002949852508</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2254,19 +2256,19 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>992</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>971</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.9788306451612904</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2300,19 +2302,19 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>948</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>933</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.9841772151898734</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2344,19 +2346,19 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>907</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>809</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.8919514884233738</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2388,19 +2390,19 @@
           <t>Atenas</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>801</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>762</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.951310861423221</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -2456,7 +2458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2538,19 +2540,19 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>1485</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>1321</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.8895622895622896</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.0006734006734006734</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -2586,19 +2588,19 @@
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>1195</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>1194</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.999163179916318</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.0008368200836820083</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -2630,19 +2632,19 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>961</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>934</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.9719042663891779</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0.001040582726326743</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2676,19 +2678,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>954</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>945</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.9905660377358491</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.001048218029350105</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2722,19 +2724,19 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>920</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>914</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.9934782608695653</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0.00108695652173913</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2768,19 +2770,19 @@
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>915</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>808</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.8830601092896175</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0.001092896174863388</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2816,19 +2818,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>801</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>799</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.9975031210986267</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.001248439450686642</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2862,19 +2864,19 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>794</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.01133501259445844</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0.001259445843828715</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2910,19 +2912,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>6292</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>6135</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.9750476795931341</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0.001271455816910362</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2956,19 +2958,19 @@
           <t>Daytona Beach Area</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>742</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>717</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.9663072776280324</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0.001347708894878706</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3020,7 +3022,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -3072,19 +3074,19 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="11" t="n">
         <v>129101</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="11" t="n">
         <v>1900</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>118516</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.9180099302096808</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.0147171594333119</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3104,19 +3106,19 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="11" t="n">
         <v>97765</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="11" t="n">
         <v>1425</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>96602</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.9881041272439012</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="12" t="n">
         <v>0.01457576842428272</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3136,19 +3138,19 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="11" t="n">
         <v>86964</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="11" t="n">
         <v>1060</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>83427</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.9593279977921899</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.01218895175014949</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3168,19 +3170,19 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="11" t="n">
         <v>23857</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="11" t="n">
         <v>455</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>17845</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.7479984910089282</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.01907197049084126</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -3200,19 +3202,19 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="11" t="n">
         <v>21888</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="11" t="n">
         <v>195</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>18204</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.8316885964912281</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="12" t="n">
         <v>0.008908991228070175</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -3232,19 +3234,19 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="11" t="n">
         <v>11890</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="11" t="n">
         <v>243</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>11698</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.983851976450799</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="12" t="n">
         <v>0.02043734230445753</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -3264,19 +3266,19 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="11" t="n">
         <v>11322</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="11" t="n">
         <v>48</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>10624</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.9383501148207031</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.004239533651298357</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3296,19 +3298,19 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="11" t="n">
         <v>7142</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="11" t="n">
         <v>135</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>6985</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.97801736208345</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.01890226827219266</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -3328,19 +3330,19 @@
           <t>Marriott</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="11" t="n">
         <v>7065</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>6811</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="12" t="n">
         <v>0.9640481245576787</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="12" t="n">
         <v>0.0008492569002123143</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -3360,19 +3362,19 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="11" t="n">
         <v>3273</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="11" t="n">
         <v>80</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>3269</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.9987778796211427</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="12" t="n">
         <v>0.02444240757714635</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -3392,19 +3394,19 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="11" t="n">
         <v>3131</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>3123</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="12" t="n">
         <v>0.9974449057809007</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="12" t="n">
         <v>0.006387735547748324</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3424,19 +3426,19 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="11" t="n">
         <v>2624</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>2502</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="12" t="n">
         <v>0.9535060975609756</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="12" t="n">
         <v>0.003429878048780488</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -3456,19 +3458,19 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="11" t="n">
         <v>2536</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="11" t="n">
         <v>41</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>2458</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="12" t="n">
         <v>0.9692429022082019</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="12" t="n">
         <v>0.01616719242902208</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -3488,19 +3490,19 @@
           <t>Palace</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="11" t="n">
         <v>2504</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="11" t="n">
         <v>59</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>2498</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="12" t="n">
         <v>0.9976038338658147</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="12" t="n">
         <v>0.02356230031948882</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -3520,19 +3522,19 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="11" t="n">
         <v>2261</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>2258</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="12" t="n">
         <v>0.9986731534719151</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="12" t="n">
         <v>0.002653693056169837</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -3552,19 +3554,19 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="11" t="n">
         <v>2110</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>2094</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.9924170616113744</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="12" t="n">
         <v>0.005213270142180095</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -3584,19 +3586,19 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="11" t="n">
         <v>2039</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="11" t="n">
         <v>167</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>2039</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="12" t="n">
         <v>0.08190289357528201</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3616,19 +3618,19 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="11" t="n">
         <v>1352</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1351</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="12" t="n">
         <v>0.9992603550295858</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="12" t="n">
         <v>0.01109467455621302</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -3648,19 +3650,19 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="11" t="n">
         <v>1342</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="11" t="n">
         <v>32</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>1256</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="12" t="n">
         <v>0.9359165424739195</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="12" t="n">
         <v>0.02384500745156483</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -3680,19 +3682,19 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="11" t="n">
         <v>1291</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="11" t="n">
         <v>17</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>1190</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="12" t="n">
         <v>0.9217660728117738</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="12" t="n">
         <v>0.01316808675445391</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3712,19 +3714,19 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="11" t="n">
         <v>1216</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="11" t="n">
         <v>16</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>1156</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="12" t="n">
         <v>0.9506578947368421</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="12" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -3744,19 +3746,19 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="11" t="n">
         <v>1176</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="11" t="n">
         <v>46</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>1174</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="12" t="n">
         <v>0.9982993197278912</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="12" t="n">
         <v>0.0391156462585034</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3776,19 +3778,19 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="11" t="n">
         <v>1101</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>799</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="12" t="n">
         <v>0.7257039055404177</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="12" t="n">
         <v>0.0009082652134423251</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3808,19 +3810,19 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="11" t="n">
         <v>1089</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="11" t="n">
         <v>100</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>988</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="12" t="n">
         <v>0.9072543617998163</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="12" t="n">
         <v>0.09182736455463728</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3840,19 +3842,19 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="11" t="n">
         <v>958</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="11" t="n">
         <v>28</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>948</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="12" t="n">
         <v>0.9895615866388309</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="12" t="n">
         <v>0.02922755741127349</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3872,19 +3874,19 @@
           <t>Best Western</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="11" t="n">
         <v>925</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>820</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="12" t="n">
         <v>0.8864864864864865</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="12" t="n">
         <v>0.005405405405405406</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3904,19 +3906,19 @@
           <t>Las Brisas</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="11" t="n">
         <v>906</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>903</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="12" t="n">
         <v>0.9966887417218543</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="12" t="n">
         <v>0.02759381898454746</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3936,19 +3938,19 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="11" t="n">
         <v>827</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>822</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="12" t="n">
         <v>0.9939540507859734</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="12" t="n">
         <v>0.0120918984280532</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3968,19 +3970,19 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="11" t="n">
         <v>714</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="11" t="n">
         <v>27</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>714</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="12" t="n">
         <v>0.03781512605042017</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4000,19 +4002,19 @@
           <t>GHL</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="11" t="n">
         <v>582</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>572</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="12" t="n">
         <v>0.9828178694158075</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="12" t="n">
         <v>0.02233676975945017</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4032,19 +4034,19 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="11" t="n">
         <v>546</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>546</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="12" t="n">
         <v>0.005494505494505495</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4064,19 +4066,19 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="11" t="n">
         <v>423</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="11" t="n">
         <v>100</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>423</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="12" t="n">
         <v>0.2364066193853428</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4096,19 +4098,19 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="11" t="n">
         <v>407</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>384</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="12" t="n">
         <v>0.9434889434889435</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="12" t="n">
         <v>0.004914004914004914</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4128,19 +4130,19 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="11" t="n">
         <v>295</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>295</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4160,19 +4162,19 @@
           <t>RIU</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="11" t="n">
         <v>290</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>290</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="12" t="n">
         <v>0.01379310344827586</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4192,19 +4194,19 @@
           <t>Americas Hotels Group</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="11" t="n">
         <v>184</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>174</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="12" t="n">
         <v>0.9456521739130435</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="12" t="n">
         <v>0.01630434782608696</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4224,19 +4226,19 @@
           <t>Hoteles Geh Suites</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="11" t="n">
         <v>182</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>182</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4256,19 +4258,19 @@
           <t>Dann</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="11" t="n">
         <v>172</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="12" t="n">
         <v>0.4593023255813953</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4288,19 +4290,19 @@
           <t>Pueblo Bonito</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="11" t="n">
         <v>168</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>168</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="12" t="n">
         <v>0.05357142857142857</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4348,7 +4350,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4400,19 +4402,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="11" t="n">
         <v>45909</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="11" t="n">
         <v>600</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>38552</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.8397481975211832</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.01306933281056002</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -4432,19 +4434,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="11" t="n">
         <v>37081</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="11" t="n">
         <v>264</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>35710</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.96302688708503</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="12" t="n">
         <v>0.00711954909522397</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -4464,19 +4466,19 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="11" t="n">
         <v>15821</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="11" t="n">
         <v>212</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15278</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.9656785285380191</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.01339991151001833</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -4496,19 +4498,19 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="11" t="n">
         <v>15562</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="11" t="n">
         <v>163</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>14903</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.957653257935998</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.01047423210384269</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -4528,19 +4530,19 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="11" t="n">
         <v>12685</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="11" t="n">
         <v>182</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>11645</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.9180134016554986</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="12" t="n">
         <v>0.01434765471028774</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -4560,19 +4562,19 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="11" t="n">
         <v>10881</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="11" t="n">
         <v>157</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>10695</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.9829059829059829</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="12" t="n">
         <v>0.01442882088043378</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -4592,19 +4594,19 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="11" t="n">
         <v>10027</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="11" t="n">
         <v>108</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>9248</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.922309763638177</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.01077091851999601</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -4624,19 +4626,19 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="11" t="n">
         <v>8361</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="11" t="n">
         <v>130</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>7073</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.8459514412151656</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.01554837938045688</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -4656,19 +4658,19 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="11" t="n">
         <v>8245</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="11" t="n">
         <v>62</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>7945</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="12" t="n">
         <v>0.9636143117040631</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="12" t="n">
         <v>0.007519708914493633</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4688,19 +4690,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="11" t="n">
         <v>7663</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="11" t="n">
         <v>49</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>7445</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.9715516116403498</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="12" t="n">
         <v>0.006394362521205794</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -4720,19 +4722,19 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="11" t="n">
         <v>7313</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="11" t="n">
         <v>87</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>7155</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="12" t="n">
         <v>0.9783946396827568</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="12" t="n">
         <v>0.0118966224531656</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -4752,19 +4754,19 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="11" t="n">
         <v>7042</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>6776</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="12" t="n">
         <v>0.9622266401590457</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="12" t="n">
         <v>0.003550127804600965</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -4784,19 +4786,19 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="11" t="n">
         <v>6553</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="11" t="n">
         <v>164</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>6428</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="12" t="n">
         <v>0.9809247672821608</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="12" t="n">
         <v>0.02502670532580498</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -4816,19 +4818,19 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="11" t="n">
         <v>5786</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="11" t="n">
         <v>67</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>5607</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="12" t="n">
         <v>0.9690632561354995</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="12" t="n">
         <v>0.01157967507777394</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -4848,19 +4850,19 @@
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="11" t="n">
         <v>5202</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="11" t="n">
         <v>73</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>5104</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="12" t="n">
         <v>0.9811610918877355</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="12" t="n">
         <v>0.01403306420607459</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -4880,19 +4882,19 @@
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="11" t="n">
         <v>5109</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="11" t="n">
         <v>42</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>4982</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.9751419064396164</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="12" t="n">
         <v>0.008220786846741044</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -4912,19 +4914,19 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="11" t="n">
         <v>4987</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="11" t="n">
         <v>228</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>4084</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="12" t="n">
         <v>0.8189292159614999</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="12" t="n">
         <v>0.04571886905955484</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -4944,19 +4946,19 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="11" t="n">
         <v>4730</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="11" t="n">
         <v>61</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>4652</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="12" t="n">
         <v>0.9835095137420719</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="12" t="n">
         <v>0.01289640591966173</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -4976,19 +4978,19 @@
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="11" t="n">
         <v>4717</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="11" t="n">
         <v>93</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>4608</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="12" t="n">
         <v>0.9768920924316302</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="12" t="n">
         <v>0.01971592113631546</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -5008,19 +5010,19 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="11" t="n">
         <v>4704</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="11" t="n">
         <v>72</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>4478</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="12" t="n">
         <v>0.9519557823129252</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="12" t="n">
         <v>0.01530612244897959</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -5040,19 +5042,19 @@
           <t>Denver (and vicinity), CO, US</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="11" t="n">
         <v>4091</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="11" t="n">
         <v>53</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>3947</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="12" t="n">
         <v>0.9648007822048399</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="12" t="n">
         <v>0.01295526766071865</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -5072,19 +5074,19 @@
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="11" t="n">
         <v>3945</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="11" t="n">
         <v>62</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>3864</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="12" t="n">
         <v>0.979467680608365</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="12" t="n">
         <v>0.01571609632446134</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -5104,19 +5106,19 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="11" t="n">
         <v>3897</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="11" t="n">
         <v>84</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>3783</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="12" t="n">
         <v>0.970746728252502</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="12" t="n">
         <v>0.02155504234026174</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -5136,19 +5138,19 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="11" t="n">
         <v>3884</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="11" t="n">
         <v>69</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>3806</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="12" t="n">
         <v>0.9799176107106076</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="12" t="n">
         <v>0.01776519052523172</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -5168,19 +5170,19 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="11" t="n">
         <v>3806</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="11" t="n">
         <v>265</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>3525</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="12" t="n">
         <v>0.9261692065160273</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="12" t="n">
         <v>0.06962690488702049</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -5200,19 +5202,19 @@
           <t>Múnich Area</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="11" t="n">
         <v>3753</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="11" t="n">
         <v>98</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>3296</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="12" t="n">
         <v>0.8782307487343458</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="12" t="n">
         <v>0.02611244337863043</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5232,19 +5234,19 @@
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="11" t="n">
         <v>3356</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="11" t="n">
         <v>134</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>3329</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="12" t="n">
         <v>0.9919547079856973</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="12" t="n">
         <v>0.03992848629320619</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -5264,19 +5266,19 @@
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="11" t="n">
         <v>3307</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>2831</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="12" t="n">
         <v>0.8560628968853946</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="12" t="n">
         <v>0.01028122165104324</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -5296,19 +5298,19 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="11" t="n">
         <v>3285</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="11" t="n">
         <v>59</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>3150</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="12" t="n">
         <v>0.958904109589041</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="12" t="n">
         <v>0.01796042617960426</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -5328,19 +5330,19 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="11" t="n">
         <v>3182</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="11" t="n">
         <v>49</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>2778</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="12" t="n">
         <v>0.8730358265241986</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="12" t="n">
         <v>0.01539912005028284</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -5360,19 +5362,19 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="11" t="n">
         <v>3115</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="11" t="n">
         <v>46</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>3004</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="12" t="n">
         <v>0.9643659711075442</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="12" t="n">
         <v>0.01476725521669342</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -5392,19 +5394,19 @@
           <t>Hamburg Area</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="11" t="n">
         <v>3025</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="11" t="n">
         <v>40</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>2933</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="12" t="n">
         <v>0.9695867768595041</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="12" t="n">
         <v>0.01322314049586777</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -5424,19 +5426,19 @@
           <t>Vienna Area</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="11" t="n">
         <v>2953</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="11" t="n">
         <v>45</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>2849</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="12" t="n">
         <v>0.964781578056214</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="12" t="n">
         <v>0.01523874026413817</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -5456,19 +5458,19 @@
           <t>Budapest Area</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="11" t="n">
         <v>2885</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>2790</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="12" t="n">
         <v>0.9670710571923743</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="12" t="n">
         <v>0.004506065857885615</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -5488,19 +5490,19 @@
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="11" t="n">
         <v>2879</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="11" t="n">
         <v>68</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>2571</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="12" t="n">
         <v>0.8930184091698506</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="12" t="n">
         <v>0.02361931226120181</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -5520,19 +5522,19 @@
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="11" t="n">
         <v>2870</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>2790</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="12" t="n">
         <v>0.9721254355400697</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="12" t="n">
         <v>0.003484320557491289</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -5552,19 +5554,19 @@
           <t>Montreal</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="11" t="n">
         <v>2813</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>2428</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="12" t="n">
         <v>0.8631354425879844</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="12" t="n">
         <v>0.004265908282971916</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -5584,19 +5586,19 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="11" t="n">
         <v>2781</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>2718</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="12" t="n">
         <v>0.9773462783171522</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="12" t="n">
         <v>0.003236245954692557</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -5616,19 +5618,19 @@
           <t>San Diego</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="11" t="n">
         <v>2762</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="11" t="n">
         <v>24</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>2487</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="12" t="n">
         <v>0.9004344677769732</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="12" t="n">
         <v>0.008689355539464157</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -5648,19 +5650,19 @@
           <t>Phoenix (and vicinity), AZ, US</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="11" t="n">
         <v>2727</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="11" t="n">
         <v>53</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>2657</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="12" t="n">
         <v>0.9743307664099743</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="12" t="n">
         <v>0.01943527686101943</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -5680,19 +5682,19 @@
           <t>Pittsburgh Area</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="11" t="n">
         <v>2669</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="11" t="n">
         <v>61</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>2588</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="12" t="n">
         <v>0.9696515548894717</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="12" t="n">
         <v>0.02285500187336081</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -5712,19 +5714,19 @@
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="11" t="n">
         <v>2576</v>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="11" t="n">
         <v>32</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>2418</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="12" t="n">
         <v>0.9386645962732919</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="12" t="n">
         <v>0.0124223602484472</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -5744,19 +5746,19 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="11" t="n">
         <v>2529</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>2114</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="12" t="n">
         <v>0.8359035191775406</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="12" t="n">
         <v>0.005140371688414393</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -5776,19 +5778,19 @@
           <t>Cleveland Area</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="11" t="n">
         <v>2157</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="11" t="n">
         <v>37</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>2137</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="12" t="n">
         <v>0.990727862772369</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="12" t="n">
         <v>0.01715345387111729</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -5808,19 +5810,19 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="11" t="n">
         <v>2140</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>2088</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="12" t="n">
         <v>0.9757009345794393</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="12" t="n">
         <v>0.005607476635514018</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5840,19 +5842,19 @@
           <t>Ottawa Area</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="11" t="n">
         <v>2082</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="11" t="n">
         <v>72</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>1913</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="12" t="n">
         <v>0.9188280499519692</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="12" t="n">
         <v>0.0345821325648415</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5872,19 +5874,19 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="11" t="n">
         <v>2016</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>1943</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="12" t="n">
         <v>0.9637896825396826</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="12" t="n">
         <v>0.006448412698412698</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5904,19 +5906,19 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="11" t="n">
         <v>1996</v>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>1975</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="12" t="n">
         <v>0.9894789579158316</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="12" t="n">
         <v>0.00501002004008016</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5936,19 +5938,19 @@
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="11" t="n">
         <v>1935</v>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="11" t="n">
         <v>139</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>1868</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="12" t="n">
         <v>0.9653746770025839</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F54" s="12" t="n">
         <v>0.07183462532299742</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5968,19 +5970,19 @@
           <t>Atenas</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="11" t="n">
         <v>1862</v>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>1706</v>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="E55" s="12" t="n">
         <v>0.916219119226638</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="12" t="n">
         <v>0.001611170784103115</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -6000,19 +6002,19 @@
           <t>London Area</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="11" t="n">
         <v>1843</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="11" t="n">
         <v>16</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>1694</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="12" t="n">
         <v>0.919153553988063</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="12" t="n">
         <v>0.008681497558328812</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -6032,19 +6034,19 @@
           <t>Washington, DC Area</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="11" t="n">
         <v>1830</v>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="11" t="n">
         <v>45</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>1753</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="12" t="n">
         <v>0.9579234972677596</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F57" s="12" t="n">
         <v>0.02459016393442623</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -6064,19 +6066,19 @@
           <t>Greater Glasgow Area</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="11" t="n">
         <v>1790</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="11" t="n">
         <v>18</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>1641</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="12" t="n">
         <v>0.9167597765363128</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="12" t="n">
         <v>0.01005586592178771</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -6096,19 +6098,19 @@
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="11" t="n">
         <v>1677</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="11" t="n">
         <v>21</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>1475</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="12" t="n">
         <v>0.8795468097793679</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="12" t="n">
         <v>0.01252236135957066</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -6128,19 +6130,19 @@
           <t>Philadelphia (and vicinity), PA, US</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="11" t="n">
         <v>1611</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="11" t="n">
         <v>28</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="12" t="n">
         <v>0.9745499689633768</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F60" s="12" t="n">
         <v>0.01738050900062073</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -6160,19 +6162,19 @@
           <t>Berlin Area</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="11" t="n">
         <v>1602</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>1488</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="12" t="n">
         <v>0.9288389513108615</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="12" t="n">
         <v>0.01560549313358302</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -6192,19 +6194,19 @@
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="11" t="n">
         <v>1559</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="11" t="n">
         <v>23</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>1263</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="12" t="n">
         <v>0.8101347017318794</v>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="F62" s="12" t="n">
         <v>0.01475304682488775</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -6224,19 +6226,19 @@
           <t>Antalya Area</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="11" t="n">
         <v>1543</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>1527</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="12" t="n">
         <v>0.9896305897602073</v>
       </c>
-      <c r="F63" s="5" t="n">
+      <c r="F63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -6256,19 +6258,19 @@
           <t>Minneapolis - St. Paul Area</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="11" t="n">
         <v>1542</v>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>1477</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="12" t="n">
         <v>0.9578469520103762</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="F64" s="12" t="n">
         <v>0.01297016861219196</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -6288,19 +6290,19 @@
           <t>Jakarta Area</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="11" t="n">
         <v>1534</v>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>1475</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="12" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="12" t="n">
         <v>0.007822685788787484</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -6320,19 +6322,19 @@
           <t>Omaha Area</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="11" t="n">
         <v>1471</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>1442</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="12" t="n">
         <v>0.9802855200543847</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="12" t="n">
         <v>0.01699524133242692</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -6352,19 +6354,19 @@
           <t>Los Cabos Area</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="11" t="n">
         <v>1469</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="11" t="n">
         <v>14</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>1459</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="12" t="n">
         <v>0.9931926480599047</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F67" s="12" t="n">
         <v>0.009530292716133424</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -6384,19 +6386,19 @@
           <t>Quebec</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="11" t="n">
         <v>1421</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="11" t="n">
         <v>16</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>1384</v>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E68" s="12" t="n">
         <v>0.9739619985925405</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="12" t="n">
         <v>0.01125967628430683</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -6416,19 +6418,19 @@
           <t>Hawái</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="11" t="n">
         <v>1408</v>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="11" t="n">
         <v>14</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>1271</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="12" t="n">
         <v>0.9026988636363636</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="F69" s="12" t="n">
         <v>0.009943181818181818</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -6448,19 +6450,19 @@
           <t>Okanagan Valley Area</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="11" t="n">
         <v>1375</v>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="11" t="n">
         <v>17</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>1250</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="12" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F70" s="12" t="n">
         <v>0.01236363636363636</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -6480,19 +6482,19 @@
           <t>Aruba</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="11" t="n">
         <v>1363</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C71" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>1300</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="12" t="n">
         <v>0.9537784299339692</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="12" t="n">
         <v>0.008804108584005869</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6512,19 +6514,19 @@
           <t>Fráncfort</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n">
+      <c r="B72" s="11" t="n">
         <v>1348</v>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C72" s="11" t="n">
         <v>21</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>1282</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="12" t="n">
         <v>0.9510385756676558</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F72" s="12" t="n">
         <v>0.0155786350148368</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -6544,19 +6546,19 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="B73" s="5" t="n">
+      <c r="B73" s="11" t="n">
         <v>1331</v>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C73" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>1268</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="12" t="n">
         <v>0.9526671675432006</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="12" t="n">
         <v>0.003005259203606311</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -6576,19 +6578,19 @@
           <t>Tampa Area</t>
         </is>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="11" t="n">
         <v>1316</v>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="11" t="n">
         <v>22</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>1268</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="12" t="n">
         <v>0.9635258358662614</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="12" t="n">
         <v>0.01671732522796352</v>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -6608,19 +6610,19 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="11" t="n">
         <v>1311</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C75" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>1228</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="12" t="n">
         <v>0.9366895499618612</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F75" s="12" t="n">
         <v>0.007627765064836003</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -6640,19 +6642,19 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="11" t="n">
         <v>1292</v>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C76" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>1291</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="12" t="n">
         <v>0.9992260061919505</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F76" s="12" t="n">
         <v>0.01006191950464396</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -6672,19 +6674,19 @@
           <t>Provence Area</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="11" t="n">
         <v>1272</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>1241</v>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E77" s="12" t="n">
         <v>0.97562893081761</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="12" t="n">
         <v>0.001572327044025157</v>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -6704,19 +6706,19 @@
           <t>Manchester Area</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="11" t="n">
         <v>1249</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C78" s="11" t="n">
         <v>24</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>1181</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E78" s="12" t="n">
         <v>0.9455564451561249</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="12" t="n">
         <v>0.01921537229783827</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -6736,19 +6738,19 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="11" t="n">
         <v>1151</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C79" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>1062</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="12" t="n">
         <v>0.9226759339704604</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="12" t="n">
         <v>0.005212858384013901</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -6768,19 +6770,19 @@
           <t>Munich Area</t>
         </is>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B80" s="11" t="n">
         <v>1147</v>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="11" t="n">
         <v>22</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>1140</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="12" t="n">
         <v>0.993897122929381</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="12" t="n">
         <v>0.01918047079337402</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -6800,19 +6802,19 @@
           <t>Panama City Area</t>
         </is>
       </c>
-      <c r="B81" s="5" t="n">
+      <c r="B81" s="11" t="n">
         <v>1137</v>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C81" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>1038</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E81" s="12" t="n">
         <v>0.9129287598944591</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="12" t="n">
         <v>0.0079155672823219</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -6832,19 +6834,19 @@
           <t>Columbus (and vicinity), OH, US</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n">
+      <c r="B82" s="11" t="n">
         <v>1112</v>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C82" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>1075</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E82" s="12" t="n">
         <v>0.966726618705036</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F82" s="12" t="n">
         <v>0.02248201438848921</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -6864,19 +6866,19 @@
           <t>Salt Lake City Area</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n">
+      <c r="B83" s="11" t="n">
         <v>1057</v>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C83" s="11" t="n">
         <v>30</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>1022</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="E83" s="12" t="n">
         <v>0.9668874172185431</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F83" s="12" t="n">
         <v>0.02838221381267739</v>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -6896,19 +6898,19 @@
           <t>Monterey Area</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n">
+      <c r="B84" s="11" t="n">
         <v>1036</v>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C84" s="11" t="n">
         <v>17</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>959</v>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E84" s="12" t="n">
         <v>0.9256756756756757</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F84" s="12" t="n">
         <v>0.01640926640926641</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -6928,19 +6930,19 @@
           <t>Naples Area</t>
         </is>
       </c>
-      <c r="B85" s="5" t="n">
+      <c r="B85" s="11" t="n">
         <v>1016</v>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C85" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>887</v>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E85" s="12" t="n">
         <v>0.8730314960629921</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F85" s="12" t="n">
         <v>0.000984251968503937</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -6960,19 +6962,19 @@
           <t>Bogotá Area</t>
         </is>
       </c>
-      <c r="B86" s="5" t="n">
+      <c r="B86" s="11" t="n">
         <v>977</v>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>586</v>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="E86" s="12" t="n">
         <v>0.5997952917093142</v>
       </c>
-      <c r="F86" s="5" t="n">
+      <c r="F86" s="12" t="n">
         <v>0.004094165813715456</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -6992,19 +6994,19 @@
           <t>Key West Area</t>
         </is>
       </c>
-      <c r="B87" s="5" t="n">
+      <c r="B87" s="11" t="n">
         <v>955</v>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>943</v>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E87" s="12" t="n">
         <v>0.987434554973822</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F87" s="12" t="n">
         <v>0.01361256544502618</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -7024,19 +7026,19 @@
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="B88" s="5" t="n">
+      <c r="B88" s="11" t="n">
         <v>912</v>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C88" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>836</v>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E88" s="12" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F88" s="12" t="n">
         <v>0.004385964912280702</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -7056,19 +7058,19 @@
           <t>Dresde Area</t>
         </is>
       </c>
-      <c r="B89" s="5" t="n">
+      <c r="B89" s="11" t="n">
         <v>894</v>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C89" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>862</v>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="E89" s="12" t="n">
         <v>0.9642058165548099</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F89" s="12" t="n">
         <v>0.01342281879194631</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -7088,19 +7090,19 @@
           <t>Malta Area</t>
         </is>
       </c>
-      <c r="B90" s="5" t="n">
+      <c r="B90" s="11" t="n">
         <v>890</v>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C90" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D90" s="5" t="n">
         <v>844</v>
       </c>
-      <c r="E90" s="5" t="n">
+      <c r="E90" s="12" t="n">
         <v>0.9483146067415731</v>
       </c>
-      <c r="F90" s="5" t="n">
+      <c r="F90" s="12" t="n">
         <v>0.006741573033707865</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -7120,19 +7122,19 @@
           <t>Da Nang Area</t>
         </is>
       </c>
-      <c r="B91" s="5" t="n">
+      <c r="B91" s="11" t="n">
         <v>877</v>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="E91" s="12" t="n">
         <v>0.8745724059293044</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F91" s="12" t="n">
         <v>0.01254275940706956</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -7152,19 +7154,19 @@
           <t>Portland (and vicinity), OR, US</t>
         </is>
       </c>
-      <c r="B92" s="5" t="n">
+      <c r="B92" s="11" t="n">
         <v>859</v>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C92" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>854</v>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="E92" s="12" t="n">
         <v>0.9941792782305006</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="12" t="n">
         <v>0.03841676367869616</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -7184,19 +7186,19 @@
           <t>Bath Area</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n">
+      <c r="B93" s="11" t="n">
         <v>851</v>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C93" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>822</v>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E93" s="12" t="n">
         <v>0.9659224441833137</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F93" s="12" t="n">
         <v>0.01175088131609871</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -7216,19 +7218,19 @@
           <t>Halifax Area</t>
         </is>
       </c>
-      <c r="B94" s="5" t="n">
+      <c r="B94" s="11" t="n">
         <v>829</v>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C94" s="11" t="n">
         <v>17</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>803</v>
       </c>
-      <c r="E94" s="5" t="n">
+      <c r="E94" s="12" t="n">
         <v>0.9686369119420989</v>
       </c>
-      <c r="F94" s="5" t="n">
+      <c r="F94" s="12" t="n">
         <v>0.02050663449939686</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -7248,19 +7250,19 @@
           <t>Calgary Area</t>
         </is>
       </c>
-      <c r="B95" s="5" t="n">
+      <c r="B95" s="11" t="n">
         <v>826</v>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C95" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>817</v>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E95" s="12" t="n">
         <v>0.9891041162227603</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F95" s="12" t="n">
         <v>0.01452784503631961</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -7280,19 +7282,19 @@
           <t>Kansas City (and vicinity), MO, US</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n">
+      <c r="B96" s="11" t="n">
         <v>801</v>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>727</v>
       </c>
-      <c r="E96" s="5" t="n">
+      <c r="E96" s="12" t="n">
         <v>0.9076154806491885</v>
       </c>
-      <c r="F96" s="5" t="n">
+      <c r="F96" s="12" t="n">
         <v>0.01373283395755306</v>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -7312,19 +7314,19 @@
           <t>Charlotte Area</t>
         </is>
       </c>
-      <c r="B97" s="5" t="n">
+      <c r="B97" s="11" t="n">
         <v>767</v>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="11" t="n">
         <v>26</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>760</v>
       </c>
-      <c r="E97" s="5" t="n">
+      <c r="E97" s="12" t="n">
         <v>0.9908735332464146</v>
       </c>
-      <c r="F97" s="5" t="n">
+      <c r="F97" s="12" t="n">
         <v>0.03389830508474576</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -7344,19 +7346,19 @@
           <t>Jacksonville Area</t>
         </is>
       </c>
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="11" t="n">
         <v>755</v>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="11" t="n">
         <v>17</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>731</v>
       </c>
-      <c r="E98" s="5" t="n">
+      <c r="E98" s="12" t="n">
         <v>0.9682119205298013</v>
       </c>
-      <c r="F98" s="5" t="n">
+      <c r="F98" s="12" t="n">
         <v>0.02251655629139073</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -7376,19 +7378,19 @@
           <t>Daytona Beach Area</t>
         </is>
       </c>
-      <c r="B99" s="5" t="n">
+      <c r="B99" s="11" t="n">
         <v>742</v>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C99" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>717</v>
       </c>
-      <c r="E99" s="5" t="n">
+      <c r="E99" s="12" t="n">
         <v>0.9663072776280324</v>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="F99" s="12" t="n">
         <v>0.001347708894878706</v>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -7408,19 +7410,19 @@
           <t>North Yorkshire Area</t>
         </is>
       </c>
-      <c r="B100" s="5" t="n">
+      <c r="B100" s="11" t="n">
         <v>735</v>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C100" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>689</v>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E100" s="12" t="n">
         <v>0.9374149659863945</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F100" s="12" t="n">
         <v>0.004081632653061225</v>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -7440,19 +7442,19 @@
           <t>Hampton Roads</t>
         </is>
       </c>
-      <c r="B101" s="5" t="n">
+      <c r="B101" s="11" t="n">
         <v>714</v>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C101" s="11" t="n">
         <v>17</v>
       </c>
       <c r="D101" s="5" t="n">
         <v>714</v>
       </c>
-      <c r="E101" s="5" t="n">
+      <c r="E101" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="F101" s="12" t="n">
         <v>0.02380952380952381</v>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -7472,19 +7474,19 @@
           <t>Phu Quoc Island Area</t>
         </is>
       </c>
-      <c r="B102" s="5" t="n">
+      <c r="B102" s="11" t="n">
         <v>710</v>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C102" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>651</v>
       </c>
-      <c r="E102" s="5" t="n">
+      <c r="E102" s="12" t="n">
         <v>0.9169014084507042</v>
       </c>
-      <c r="F102" s="5" t="n">
+      <c r="F102" s="12" t="n">
         <v>0.01690140845070422</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -7504,19 +7506,19 @@
           <t>Cardiff Area</t>
         </is>
       </c>
-      <c r="B103" s="5" t="n">
+      <c r="B103" s="11" t="n">
         <v>708</v>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C103" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>664</v>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E103" s="12" t="n">
         <v>0.9378531073446328</v>
       </c>
-      <c r="F103" s="5" t="n">
+      <c r="F103" s="12" t="n">
         <v>0.01412429378531073</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -7536,19 +7538,19 @@
           <t>Kingston Area</t>
         </is>
       </c>
-      <c r="B104" s="5" t="n">
+      <c r="B104" s="11" t="n">
         <v>699</v>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C104" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>670</v>
       </c>
-      <c r="E104" s="5" t="n">
+      <c r="E104" s="12" t="n">
         <v>0.9585121602288984</v>
       </c>
-      <c r="F104" s="5" t="n">
+      <c r="F104" s="12" t="n">
         <v>0.01573676680972818</v>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -7568,19 +7570,19 @@
           <t>Milwaukee Area</t>
         </is>
       </c>
-      <c r="B105" s="5" t="n">
+      <c r="B105" s="11" t="n">
         <v>696</v>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C105" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>683</v>
       </c>
-      <c r="E105" s="5" t="n">
+      <c r="E105" s="12" t="n">
         <v>0.9813218390804598</v>
       </c>
-      <c r="F105" s="5" t="n">
+      <c r="F105" s="12" t="n">
         <v>0.02155172413793104</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -7628,7 +7630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7680,19 +7682,19 @@
           <t>DerbySoft</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="11" t="n">
         <v>329607</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="11" t="n">
         <v>4509</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>313773</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.951960971702664</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.01367992791415231</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -7712,19 +7714,19 @@
           <t>HBSI</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="11" t="n">
         <v>43864</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="11" t="n">
         <v>497</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>36287</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.827261535655663</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="12" t="n">
         <v>0.01133047601677914</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -7744,19 +7746,19 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="11" t="n">
         <v>40170</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="11" t="n">
         <v>910</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>37198</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.9260144386357979</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.0226537216828479</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -7776,19 +7778,19 @@
           <t>Expedia</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="11" t="n">
         <v>10621</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>9797</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.9224178514264194</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.0008473778363619244</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -7808,19 +7810,19 @@
           <t>SynXis</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="11" t="n">
         <v>5892</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="11" t="n">
         <v>98</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>5682</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.9643584521384929</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="12" t="n">
         <v>0.01663272233536999</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -7840,19 +7842,19 @@
           <t>Siteminder</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="11" t="n">
         <v>2237</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="11" t="n">
         <v>168</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>2237</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="12" t="n">
         <v>0.07510058113544926</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -7872,19 +7874,19 @@
           <t>HotelBeds</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="11" t="n">
         <v>619</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>605</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.9773828756058158</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.004846526655896607</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -7904,19 +7906,19 @@
           <t>Travelclick</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="11" t="n">
         <v>608</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="11" t="n">
         <v>122</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>608</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.2006578947368421</v>
       </c>
       <c r="G13" s="5" t="inlineStr">

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_OP_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
